--- a/Templates/Templates/Partlist.xlsx
+++ b/Templates/Templates/Partlist.xlsx
@@ -154,6 +154,9 @@
     <x:t>Material</x:t>
   </x:si>
   <x:si>
+    <x:t>Color [A=40, R=128, G=128, B=198]</x:t>
+  </x:si>
+  <x:si>
     <x:t>transp</x:t>
   </x:si>
   <x:si>
@@ -178,6 +181,9 @@
     <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 30.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [L:300, W:140, H:6]</x:t>
   </x:si>
   <x:si>
+    <x:t>Color [A=255, R=128, G=128, B=128]</x:t>
+  </x:si>
+  <x:si>
     <x:t>grey</x:t>
   </x:si>
   <x:si>
@@ -550,6 +556,9 @@
     <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 36.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:8, R:20]</x:t>
   </x:si>
   <x:si>
+    <x:t>Color [A=255, R=137, G=207, B=240]</x:t>
+  </x:si>
+  <x:si>
     <x:t>lightBlue</x:t>
   </x:si>
   <x:si>
@@ -589,12 +598,24 @@
     <x:t xml:space="preserve">One Roller for Omnie Wheel </x:t>
   </x:si>
   <x:si>
+    <x:t>Color [A=255, R=1, G=1, B=1]</x:t>
+  </x:si>
+  <x:si>
     <x:t>black</x:t>
   </x:si>
   <x:si>
     <x:t>Mecanum_Rolle_1.stl</x:t>
   </x:si>
   <x:si>
+    <x:t>MQTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Communication</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Comunication Platform for MQTT</x:t>
+  </x:si>
+  <x:si>
     <x:t>Omni-Wheel</x:t>
   </x:si>
   <x:si>
@@ -688,6 +709,15 @@
     <x:t>Pin for Roller in Omni-Wheel</x:t>
   </x:si>
   <x:si>
+    <x:t>OPC/UA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Comunication Platform for OPC/UA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPC_UA</x:t>
+  </x:si>
+  <x:si>
     <x:t>Regular-Wheel</x:t>
   </x:si>
   <x:si>
@@ -832,6 +862,9 @@
     <x:t>JointType: Fixed,  (XYZ) [15.00, 0.00, 0.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [L:42, W:42, H:64]</x:t>
   </x:si>
   <x:si>
+    <x:t>Color [A=100, R=128, G=128, B=128]</x:t>
+  </x:si>
+  <x:si>
     <x:t>white</x:t>
   </x:si>
   <x:si>
@@ -844,6 +877,9 @@
     <x:t>JointType: Fixed,  (XYZ) [15.00, 0.00, 0.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [L:50, W:45, H:64]</x:t>
   </x:si>
   <x:si>
+    <x:t>Color [A=100, R=188, G=128, B=128]</x:t>
+  </x:si>
+  <x:si>
     <x:t>flex</x:t>
   </x:si>
   <x:si>
@@ -857,9 +893,6 @@
   </x:si>
   <x:si>
     <x:t>uRos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Communication</x:t>
   </x:si>
   <x:si>
     <x:t>The Comunication Platform for Micro Ros</x:t>
@@ -956,8 +989,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartListTable" displayName="PartListTable" ref="A4:W114" totalsRowShown="0">
-  <x:autoFilter ref="A4:W114"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartListTable" displayName="PartListTable" ref="A4:W116" totalsRowShown="0">
+  <x:autoFilter ref="A4:W116"/>
   <x:tableColumns count="23">
     <x:tableColumn id="1" name="LEVEL"/>
     <x:tableColumn id="2" name="Name"/>
@@ -1275,7 +1308,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:W114"/>
+  <x:dimension ref="A1:W116"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="8.139196" style="0" customWidth="1"/>
@@ -1288,7 +1321,7 @@
     <x:col min="9" max="9" width="16.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.710625" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="21.710625" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="20.567768" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="32.567768" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="21.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="20.282054" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="11.567768" style="0" customWidth="1"/>
@@ -1357,10 +1390,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="T4" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="U4" s="0" t="s">
         <x:v>18</x:v>
@@ -1561,11 +1594,14 @@
       <x:c r="I12" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="P12" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q12" s="0" t="s">
         <x:v>44</x:v>
@@ -1585,16 +1621,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U13" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V13" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:23">
@@ -1602,16 +1638,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>0</x:v>
@@ -1622,23 +1658,26 @@
       <x:c r="I14" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M14" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P14" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="Q14" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="P14" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="Q14" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="U14" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V14" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W14" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:23">
@@ -1646,19 +1685,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U15" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V15" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:23">
@@ -1666,28 +1705,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G16" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q16" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="U16" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V16" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="W16" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:23">
@@ -1695,28 +1734,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q17" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="U17" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V17" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="W17" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:23">
@@ -1724,13 +1763,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>0</x:v>
@@ -1741,11 +1780,14 @@
       <x:c r="I18" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M18" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P18" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="Q18" s="0" t="s">
         <x:v>30</x:v>
@@ -1754,10 +1796,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V18" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="W18" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:23">
@@ -1765,19 +1807,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="U19" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V19" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:23">
@@ -1785,16 +1827,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G20" s="0">
         <x:v>0</x:v>
@@ -1805,11 +1847,14 @@
       <x:c r="I20" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L20" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M20" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P20" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="Q20" s="0" t="s">
         <x:v>30</x:v>
@@ -1818,10 +1863,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V20" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="W20" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:23">
@@ -1829,13 +1874,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
         <x:v>43</x:v>
@@ -1849,11 +1894,14 @@
       <x:c r="I21" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L21" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M21" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P21" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q21" s="0" t="s">
         <x:v>30</x:v>
@@ -1862,10 +1910,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V21" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="W21" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:23">
@@ -1873,7 +1921,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>26</x:v>
@@ -1887,11 +1935,14 @@
       <x:c r="I22" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L22" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M22" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P22" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="Q22" s="0" t="s">
         <x:v>30</x:v>
@@ -1900,10 +1951,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V22" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="W22" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:23">
@@ -1911,19 +1962,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="U23" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V23" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:23">
@@ -1931,16 +1982,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>0</x:v>
@@ -1951,11 +2002,14 @@
       <x:c r="I24" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L24" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M24" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P24" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="Q24" s="0" t="s">
         <x:v>30</x:v>
@@ -1964,10 +2018,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V24" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="W24" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:23">
@@ -1975,16 +2029,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>0</x:v>
@@ -1995,11 +2049,14 @@
       <x:c r="I25" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L25" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M25" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P25" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Q25" s="0" t="s">
         <x:v>30</x:v>
@@ -2008,10 +2065,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V25" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="W25" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:23">
@@ -2019,31 +2076,34 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L26" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M26" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P26" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Q26" s="0" t="s">
         <x:v>30</x:v>
@@ -2052,10 +2112,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V26" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="W26" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:23">
@@ -2063,16 +2123,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="U27" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V27" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:23">
@@ -2086,7 +2146,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>0</x:v>
@@ -2101,10 +2161,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V28" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="W28" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="W28" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:23">
@@ -2112,7 +2172,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>35</x:v>
@@ -2121,7 +2181,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="V29" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:23">
@@ -2135,7 +2195,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>0</x:v>
@@ -2150,10 +2210,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V30" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="W30" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:23">
@@ -2161,16 +2221,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="U31" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V31" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:23">
@@ -2178,13 +2238,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>0</x:v>
@@ -2199,10 +2259,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V32" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="W32" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:23">
@@ -2210,10 +2270,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>0</x:v>
@@ -2228,10 +2288,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V33" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="W33" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:23">
@@ -2239,19 +2299,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="U34" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V34" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:23">
@@ -2259,28 +2319,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q35" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="U35" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V35" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="G35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q35" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="U35" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="V35" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
       <x:c r="W35" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:23">
@@ -2288,28 +2348,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q36" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="U36" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V36" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="W36" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:23">
@@ -2317,28 +2377,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q37" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="U37" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V37" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="W37" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:23">
@@ -2346,28 +2406,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q38" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="U38" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V38" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="W38" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:23">
@@ -2375,28 +2435,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G39" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q39" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="U39" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V39" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="W39" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:23">
@@ -2404,28 +2464,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q40" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="U40" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V40" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="W40" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:23">
@@ -2433,28 +2493,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G41" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q41" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="U41" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V41" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="W41" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:23">
@@ -2462,28 +2522,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q42" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="U42" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V42" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="W42" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:23">
@@ -2491,16 +2551,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>0</x:v>
@@ -2511,23 +2571,26 @@
       <x:c r="I43" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L43" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M43" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P43" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="Q43" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="P43" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="Q43" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="U43" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V43" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="W43" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:23">
@@ -2555,11 +2618,14 @@
       <x:c r="I44" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L44" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
       <x:c r="M44" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="P44" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q44" s="0" t="s">
         <x:v>44</x:v>
@@ -2568,10 +2634,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V44" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="W44" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:23">
@@ -2579,19 +2645,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="U45" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V45" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:23">
@@ -2599,13 +2665,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>0</x:v>
@@ -2616,11 +2682,14 @@
       <x:c r="I46" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L46" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M46" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P46" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="Q46" s="0" t="s">
         <x:v>30</x:v>
@@ -2629,10 +2698,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V46" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="W46" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:23">
@@ -2640,13 +2709,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G47" s="0">
         <x:v>0</x:v>
@@ -2657,23 +2726,26 @@
       <x:c r="I47" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L47" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M47" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P47" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="Q47" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="U47" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V47" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="W47" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:23">
@@ -2681,13 +2753,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G48" s="0">
         <x:v>0</x:v>
@@ -2698,23 +2770,26 @@
       <x:c r="I48" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L48" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M48" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P48" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="Q48" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="U48" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V48" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="W48" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:23">
@@ -2722,19 +2797,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="U49" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V49" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:23">
@@ -2742,16 +2817,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>0</x:v>
@@ -2762,11 +2837,14 @@
       <x:c r="I50" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L50" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M50" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P50" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="Q50" s="0" t="s">
         <x:v>30</x:v>
@@ -2775,10 +2853,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V50" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="W50" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:23">
@@ -2786,13 +2864,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>43</x:v>
@@ -2806,23 +2884,26 @@
       <x:c r="I51" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L51" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M51" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P51" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="Q51" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="U51" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V51" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="W51" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:23">
@@ -2830,16 +2911,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>0</x:v>
@@ -2850,23 +2931,26 @@
       <x:c r="I52" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L52" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M52" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P52" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="Q52" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="U52" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V52" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="W52" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:23">
@@ -2874,16 +2958,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="U53" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V53" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:23">
@@ -2891,19 +2975,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U54" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V54" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:23">
@@ -2911,16 +2995,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>0</x:v>
@@ -2931,11 +3015,14 @@
       <x:c r="I55" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L55" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M55" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P55" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q55" s="0" t="s">
         <x:v>30</x:v>
@@ -2944,10 +3031,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V55" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="W55" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:23">
@@ -2975,11 +3062,14 @@
       <x:c r="I56" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L56" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
       <x:c r="M56" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="P56" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q56" s="0" t="s">
         <x:v>30</x:v>
@@ -2988,10 +3078,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V56" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="W56" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:23">
@@ -2999,19 +3089,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H57" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="Q57" s="0" t="s">
         <x:v>30</x:v>
@@ -3020,10 +3110,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V57" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="W57" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:23">
@@ -3031,16 +3121,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="U58" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V58" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:23">
@@ -3048,13 +3138,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>0</x:v>
@@ -3069,10 +3159,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V59" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="W59" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:23">
@@ -3080,19 +3170,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="U60" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V60" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:23">
@@ -3100,16 +3190,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>0</x:v>
@@ -3120,11 +3210,14 @@
       <x:c r="I61" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L61" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M61" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P61" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="Q61" s="0" t="s">
         <x:v>30</x:v>
@@ -3133,10 +3226,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V61" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W61" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:23">
@@ -3144,16 +3237,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>0</x:v>
@@ -3164,23 +3257,26 @@
       <x:c r="I62" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L62" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M62" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P62" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="Q62" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="U62" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V62" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W62" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:23">
@@ -3188,16 +3284,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>0</x:v>
@@ -3208,23 +3304,26 @@
       <x:c r="I63" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L63" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M63" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P63" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="Q63" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="U63" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V63" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W63" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:23">
@@ -3232,16 +3331,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>0</x:v>
@@ -3252,23 +3351,26 @@
       <x:c r="I64" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L64" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
       <x:c r="M64" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="P64" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="Q64" s="0" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="Q64" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
       <x:c r="U64" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V64" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W64" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:23">
@@ -3276,13 +3378,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
         <x:v>43</x:v>
@@ -3291,19 +3393,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H65" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="Q65" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="U65" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V65" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W65" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:23">
@@ -3311,13 +3413,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
         <x:v>43</x:v>
@@ -3331,23 +3433,26 @@
       <x:c r="I66" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L66" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M66" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P66" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="Q66" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="U66" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V66" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W66" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:23">
@@ -3355,13 +3460,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
         <x:v>43</x:v>
@@ -3378,11 +3483,14 @@
       <x:c r="I67" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L67" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
       <x:c r="M67" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="P67" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="Q67" s="0" t="s">
         <x:v>30</x:v>
@@ -3391,10 +3499,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V67" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W67" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:23">
@@ -3402,63 +3510,39 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="U68" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V68" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:23">
       <x:c r="A69" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="C69" s="0" t="s">
+      <x:c r="D69" s="0" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="D69" s="0" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="E69" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G69" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H69" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I69" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M69" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="P69" s="0" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="Q69" s="0" t="s">
-        <x:v>195</x:v>
-      </x:c>
       <x:c r="U69" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V69" s="0" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="W69" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:23">
@@ -3466,16 +3550,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>0</x:v>
@@ -3486,23 +3570,26 @@
       <x:c r="I70" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L70" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M70" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P70" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="Q70" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="U70" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V70" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="W70" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:23">
@@ -3510,16 +3597,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>0</x:v>
@@ -3530,23 +3617,26 @@
       <x:c r="I71" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L71" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M71" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P71" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="Q71" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="U71" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V71" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="W71" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:23">
@@ -3554,16 +3644,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G72" s="0">
         <x:v>0</x:v>
@@ -3574,23 +3664,26 @@
       <x:c r="I72" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L72" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M72" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P72" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="Q72" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="U72" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V72" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="W72" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:23">
@@ -3598,16 +3691,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>0</x:v>
@@ -3618,23 +3711,26 @@
       <x:c r="I73" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L73" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M73" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P73" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="Q73" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="U73" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V73" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="W73" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:23">
@@ -3642,16 +3738,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>0</x:v>
@@ -3662,23 +3758,26 @@
       <x:c r="I74" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L74" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M74" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P74" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="Q74" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="U74" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V74" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="W74" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:23">
@@ -3686,90 +3785,93 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H75" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I75" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L75" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
       <x:c r="M75" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="P75" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="Q75" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="U75" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V75" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="W75" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:23">
       <x:c r="A76" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F76" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="G76" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H76" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="I76" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L76" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
       <x:c r="M76" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="P76" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="Q76" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="U76" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V76" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="W76" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:23">
@@ -3777,13 +3879,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
         <x:v>43</x:v>
@@ -3800,114 +3902,123 @@
       <x:c r="I77" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L77" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
       <x:c r="M77" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="P77" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="Q77" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="U77" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V77" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="W77" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:23">
       <x:c r="A78" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
+      <x:c r="F78" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
       <x:c r="G78" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H78" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I78" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L78" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M78" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P78" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="Q78" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U78" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V78" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="W78" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:23">
       <x:c r="A79" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F79" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="G79" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H79" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="I79" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L79" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
       <x:c r="M79" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P79" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="Q79" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="U79" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V79" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="W79" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:23">
@@ -3915,13 +4026,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
         <x:v>43</x:v>
@@ -3938,125 +4049,116 @@
       <x:c r="I80" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L80" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
       <x:c r="M80" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P80" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="Q80" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="U80" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V80" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="W80" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:23">
       <x:c r="A81" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F81" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G81" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H81" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I81" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L81" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M81" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P81" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="Q81" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U81" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V81" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="W81" s="0" t="s">
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:23">
       <x:c r="A82" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="G82" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H82" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I82" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M82" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="P82" s="0" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="Q82" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="U82" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V82" s="0" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="W82" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:23">
       <x:c r="A83" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="G83" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H83" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I83" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M83" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="P83" s="0" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="Q83" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="U83" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V83" s="0" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="W83" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:23">
@@ -4064,13 +4166,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G84" s="0">
         <x:v>0</x:v>
@@ -4081,23 +4183,26 @@
       <x:c r="I84" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L84" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M84" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P84" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="Q84" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="U84" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V84" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="Q84" s="0" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="U84" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="V84" s="0" t="s">
-        <x:v>224</x:v>
-      </x:c>
       <x:c r="W84" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:23">
@@ -4105,13 +4210,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="G85" s="0">
         <x:v>0</x:v>
@@ -4122,23 +4227,26 @@
       <x:c r="I85" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L85" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M85" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P85" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="Q85" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="U85" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V85" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="W85" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:23">
@@ -4146,13 +4254,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>0</x:v>
@@ -4163,130 +4271,151 @@
       <x:c r="I86" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L86" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M86" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P86" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="Q86" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="U86" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V86" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="W86" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:23">
       <x:c r="A87" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G87" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H87" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I87" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L87" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M87" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P87" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="Q87" s="0" t="s">
+        <x:v>246</x:v>
       </x:c>
       <x:c r="U87" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V87" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="W87" s="0" t="s">
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:23">
       <x:c r="A88" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="G88" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H88" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I88" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L88" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="M88" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="P88" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="Q88" s="0" t="s">
+        <x:v>248</x:v>
       </x:c>
       <x:c r="U88" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V88" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="W88" s="0" t="s">
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:23">
       <x:c r="A89" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="E89" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G89" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H89" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="Q89" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="U89" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V89" s="0" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="W89" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:23">
       <x:c r="A90" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="E90" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G90" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H90" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="Q90" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="U90" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V90" s="0" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="W90" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:23">
@@ -4294,13 +4423,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G91" s="0">
         <x:v>0</x:v>
@@ -4315,30 +4447,45 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V91" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="W91" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:23">
       <x:c r="A92" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E92" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G92" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H92" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q92" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U92" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V92" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="W92" s="0" t="s">
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:23">
@@ -4346,57 +4493,51 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D93" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E93" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G93" s="0">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H93" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
       <x:c r="Q93" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U93" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V93" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="W93" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:23">
       <x:c r="A94" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D94" s="0" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="G94" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q94" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="U94" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V94" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="W94" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:23">
@@ -4404,40 +4545,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G95" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H95" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I95" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M95" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="P95" s="0" t="s">
-        <x:v>248</x:v>
-      </x:c>
       <x:c r="Q95" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="U95" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V95" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="W95" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:23">
@@ -4445,60 +4574,72 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="G96" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H96" s="0" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="I96" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M96" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="P96" s="0" t="s">
-        <x:v>252</x:v>
-      </x:c>
       <x:c r="Q96" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="U96" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V96" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="W96" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:23">
       <x:c r="A97" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G97" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H97" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I97" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L97" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M97" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P97" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="Q97" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U97" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V97" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="W97" s="0" t="s">
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:23">
@@ -4506,57 +4647,63 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="G98" s="0">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H98" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="I98" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L98" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M98" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P98" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
       <x:c r="Q98" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U98" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V98" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="W98" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:23">
       <x:c r="A99" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="G99" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q99" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="U99" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V99" s="0" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="W99" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:23">
@@ -4564,28 +4711,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="G100" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q100" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="U100" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V100" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="W100" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:23">
@@ -4593,28 +4740,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G101" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q101" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="U101" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V101" s="0" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="G101" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q101" s="0" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="U101" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="V101" s="0" t="s">
-        <x:v>253</x:v>
-      </x:c>
       <x:c r="W101" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:23">
@@ -4622,43 +4769,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="E102" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="G102" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H102" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I102" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M102" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="P102" s="0" t="s">
-        <x:v>266</x:v>
-      </x:c>
       <x:c r="Q102" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="U102" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V102" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="W102" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:23">
@@ -4666,63 +4798,75 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="E103" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H103" s="0" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="I103" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M103" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="P103" s="0" t="s">
-        <x:v>252</x:v>
-      </x:c>
       <x:c r="Q103" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="U103" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V103" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="W103" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:23">
       <x:c r="A104" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="E104" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G104" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H104" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I104" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L104" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M104" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P104" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="Q104" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U104" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V104" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="W104" s="0" t="s">
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:23">
@@ -4730,31 +4874,34 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G105" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H105" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="I105" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L105" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M105" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P105" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="Q105" s="0" t="s">
         <x:v>30</x:v>
@@ -4763,54 +4910,30 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V105" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="W105" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:23">
       <x:c r="A106" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="E106" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G106" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H106" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I106" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M106" s="0" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="P106" s="0" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="Q106" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="U106" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V106" s="0" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="W106" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:23">
@@ -4818,16 +4941,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G107" s="0">
         <x:v>0</x:v>
@@ -4838,40 +4961,73 @@
       <x:c r="I107" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L107" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M107" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P107" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="Q107" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U107" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V107" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="W107" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:23">
       <x:c r="A108" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="E108" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G108" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H108" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I108" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L108" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="M108" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="P108" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="Q108" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="U108" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V108" s="0" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="U108" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="V108" s="0" t="s">
-        <x:v>278</x:v>
+      <x:c r="W108" s="0" t="s">
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:23">
@@ -4879,13 +5035,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="E109" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>0</x:v>
@@ -4893,14 +5052,26 @@
       <x:c r="H109" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="I109" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L109" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="M109" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="P109" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
       <x:c r="Q109" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="U109" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V109" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="W109" s="0" t="s">
         <x:v>277</x:v>
@@ -4911,127 +5082,88 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="D110" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="U110" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V110" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:23">
       <x:c r="A111" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G111" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H111" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q111" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U111" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V111" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="W111" s="0" t="s">
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:23">
       <x:c r="A112" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="E112" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G112" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H112" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I112" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M112" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="P112" s="0" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="Q112" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="U112" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V112" s="0" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="W112" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:23">
       <x:c r="A113" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="E113" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G113" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H113" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I113" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M113" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="P113" s="0" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="Q113" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="U113" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V113" s="0" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="W113" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:23">
@@ -5039,16 +5171,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G114" s="0">
         <x:v>0</x:v>
@@ -5059,23 +5191,120 @@
       <x:c r="I114" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L114" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="M114" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P114" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="Q114" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U114" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V114" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="W114" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>294</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:23">
+      <x:c r="A115" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="E115" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G115" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H115" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I115" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L115" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M115" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P115" s="0" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="Q115" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U115" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V115" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="W115" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:23">
+      <x:c r="A116" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="E116" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G116" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H116" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I116" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L116" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M116" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P116" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="Q116" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="U116" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V116" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="W116" s="0" t="s">
+        <x:v>294</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Templates/Templates/Partlist.xlsx
+++ b/Templates/Templates/Partlist.xlsx
@@ -286,6 +286,9 @@
     <x:t>Ring Drive-Holder as 3D Printed Part</x:t>
   </x:si>
   <x:si>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, -32.00][mm], (RPY) [90.00, 0.00, 0.00][grad], (BOX) [H:60, R:3]</x:t>
+  </x:si>
+  <x:si>
     <x:t>adjusting ring.stl</x:t>
   </x:si>
   <x:si>
@@ -469,15 +472,12 @@
     <x:t>SensorTop_li.stl</x:t>
   </x:si>
   <x:si>
-    <x:t>Line Follower</x:t>
+    <x:t>Line-Follower</x:t>
   </x:si>
   <x:si>
     <x:t>AuxSensor</x:t>
   </x:si>
   <x:si>
-    <x:t>Line-Follower</x:t>
-  </x:si>
-  <x:si>
     <x:t>Screws</x:t>
   </x:si>
   <x:si>
@@ -505,6 +505,9 @@
     <x:t>The Wheel of the Robot</x:t>
   </x:si>
   <x:si>
+    <x:t>Mecanum-Wheel-left - Kopie</x:t>
+  </x:si>
+  <x:si>
     <x:t>Wheel-Hub</x:t>
   </x:si>
   <x:si>
@@ -529,84 +532,111 @@
     <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 6.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:32, R:2]</x:t>
   </x:si>
   <x:si>
+    <x:t>mecanumWheel_2a_pin.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rimm-outerr</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rimm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 38.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:32, R:2]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mecanumWheel_2b_pin24.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wheel-Hub-Cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HubCap</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hub Cup for Mecanum-Wheel as 3D Printed Part</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 36.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:8, R:20]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Color [A=255, R=137, G=207, B=240]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lightBlue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hub_Cup_8.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rollers</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assembly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Complete Roller Assembly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9, RotZ, alfa=-45°, r=40mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Continuous,  (XYZ) [0.00, 0.00, 20.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:32, R:12]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RollerPin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 12.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:32, R:12]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pin_Roller.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Roller</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tire</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">One Roller for Omnie Wheel </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Color [A=255, R=1, G=1, B=1]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>black</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mecanum_Rolle_1.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assembly: Mecanum-Wheel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mecanum-Wheel-left</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DHBW CAD-Data\MecanumWheel\STL-Step-Files\mecanumWheel_2b_pin24.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DHBW CAD-Data\OmniWheel\STL-Step-Dateien\Pin_Roller.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>DHBW CAD-Data\MecanumWheel\STL-Step-Files\Mecanum_Rolle_1.stl</x:t>
+  </x:si>
+  <x:si>
     <x:t>mecanumWheel_1a_pin.stl</x:t>
   </x:si>
   <x:si>
-    <x:t>rimm-outerr</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rimm</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 38.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:32, R:2]</x:t>
-  </x:si>
-  <x:si>
     <x:t>mecanumWheel_1b_pin24.stl</x:t>
   </x:si>
   <x:si>
-    <x:t>Wheel-Hub-Cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HubCap</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hub Cup for Mecanum-Wheel as 3D Printed Part</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 36.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:8, R:20]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Color [A=255, R=137, G=207, B=240]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lightBlue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hub_Cup_8.stl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rollers</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assembly</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Complete Roller Assembly</x:t>
-  </x:si>
-  <x:si>
     <x:t>9, RotZ, alfa=45°, r=40mm</x:t>
   </x:si>
   <x:si>
-    <x:t>JointType: Continuous,  (XYZ) [0.00, 0.00, 20.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:32, R:12]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RollerPin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 12.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:32, R:12]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pin_Roller.stl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Roller</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tire</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">One Roller for Omnie Wheel </x:t>
-  </x:si>
-  <x:si>
-    <x:t>Color [A=255, R=1, G=1, B=1]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>black</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mecanum_Rolle_1.stl</x:t>
-  </x:si>
-  <x:si>
     <x:t>MQTT</x:t>
   </x:si>
   <x:si>
@@ -814,7 +844,7 @@
     <x:t>Lopkalisierung für Sensor 1 ganz links</x:t>
   </x:si>
   <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [15.00, 65.00, 32.00][mm], (RPY) [15.00, 90.00, 0.00][grad], (BOX) [H:30, R:20]</x:t>
+    <x:t>JointType: Fixed,  (XYZ) [15.00, 65.00, 32.00][mm], (RPY) [90.00, 105.00, 0.00][grad], (BOX) [H:30, R:20]</x:t>
   </x:si>
   <x:si>
     <x:t>Lopkalisierung für Sensor 2 mitte links</x:t>
@@ -838,7 +868,7 @@
     <x:t>Lopkalisierung für Sensor 4 ganz rechts</x:t>
   </x:si>
   <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [15.00, -65.00, 32.00][mm], (RPY) [-15.00, 90.00, 0.00][grad], (BOX) [H:30, R:20]</x:t>
+    <x:t>JointType: Fixed,  (XYZ) [15.00, -65.00, 32.00][mm], (RPY) [-90.00, 105.00, 0.00][grad], (BOX) [H:30, R:20]</x:t>
   </x:si>
   <x:si>
     <x:t>sbFront</x:t>
@@ -901,25 +931,28 @@
     <x:t>US-Sensor</x:t>
   </x:si>
   <x:si>
+    <x:t>SensorBaseUS.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sensor pcb for US-Sensor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hc_sr04pcb.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SensorCover pcb for US-Sensor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 20.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:30, R:20]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SensorTopUS.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US_Sensor</x:t>
+  </x:si>
+  <x:si>
     <x:t>US_Sensor_hc_Sr04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SensorBaseUS.stl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sensor pcb for US-Sensor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hc_sr04pcb.stl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SensorCover pcb for US-Sensor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 20.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:30, R:20]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SensorTopUS.stl</x:t>
   </x:si>
   <x:si>
     <x:t>Column19</x:t>
@@ -989,8 +1022,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartListTable" displayName="PartListTable" ref="A4:W116" totalsRowShown="0">
-  <x:autoFilter ref="A4:W116"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartListTable" displayName="PartListTable" ref="A4:W140" totalsRowShown="0">
+  <x:autoFilter ref="A4:W140"/>
   <x:tableColumns count="23">
     <x:tableColumn id="1" name="LEVEL"/>
     <x:tableColumn id="2" name="Name"/>
@@ -1308,13 +1341,13 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:W116"/>
+  <x:dimension ref="A1:W140"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="8.139196" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22.567768" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="15.282054" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="47.282054" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="72.567768" style="0" customWidth="1"/>
     <x:col min="5" max="6" width="12.567768" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="4.996339" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="32.139196" style="0" customWidth="1"/>
@@ -1330,8 +1363,8 @@
     <x:col min="18" max="18" width="13.424911" style="0" customWidth="1"/>
     <x:col min="19" max="20" width="12.282054" style="0" customWidth="1"/>
     <x:col min="21" max="21" width="18.282054" style="0" customWidth="1"/>
-    <x:col min="22" max="22" width="18.710625" style="0" customWidth="1"/>
-    <x:col min="23" max="23" width="16.853482" style="0" customWidth="1"/>
+    <x:col min="22" max="22" width="26.424911" style="0" customWidth="1"/>
+    <x:col min="23" max="23" width="25.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="4" spans="1:23">
@@ -1390,10 +1423,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="T4" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="U4" s="0" t="s">
         <x:v>18</x:v>
@@ -2056,10 +2089,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P25" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="Q25" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="Q25" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="U25" s="0" t="s">
         <x:v>28</x:v>
@@ -2076,7 +2109,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>88</x:v>
@@ -2091,7 +2124,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
         <x:v>45</x:v>
@@ -2103,10 +2136,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P26" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="Q26" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="Q26" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="U26" s="0" t="s">
         <x:v>28</x:v>
@@ -2123,16 +2156,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="U27" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V27" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:23">
@@ -2146,7 +2179,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>0</x:v>
@@ -2161,10 +2194,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V28" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="W28" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:23">
@@ -2172,7 +2205,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>35</x:v>
@@ -2181,7 +2214,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="V29" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:23">
@@ -2195,7 +2228,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>0</x:v>
@@ -2210,10 +2243,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V30" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="W30" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:23">
@@ -2221,16 +2254,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="U31" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V31" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:23">
@@ -2238,13 +2271,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>0</x:v>
@@ -2259,10 +2292,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V32" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="W32" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:23">
@@ -2270,7 +2303,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>69</x:v>
@@ -2288,10 +2321,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V33" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="W33" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:23">
@@ -2299,19 +2332,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="U34" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V34" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:23">
@@ -2319,28 +2352,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q35" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="U35" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V35" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W35" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:23">
@@ -2348,28 +2381,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q36" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="U36" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V36" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W36" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:23">
@@ -2377,28 +2410,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q37" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="U37" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V37" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W37" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:23">
@@ -2406,28 +2439,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q38" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="U38" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V38" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W38" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:23">
@@ -2435,28 +2468,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G39" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q39" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="U39" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V39" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W39" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:23">
@@ -2464,28 +2497,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q40" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="U40" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V40" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W40" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:23">
@@ -2493,28 +2526,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G41" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q41" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="U41" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V41" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W41" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:23">
@@ -2522,28 +2555,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q42" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="U42" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V42" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W42" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:23">
@@ -2587,10 +2620,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V43" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W43" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:23">
@@ -2634,10 +2667,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V44" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W44" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:23">
@@ -2645,10 +2678,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>74</x:v>
@@ -2657,7 +2690,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="V45" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:23">
@@ -2665,13 +2698,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>0</x:v>
@@ -2689,7 +2722,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P46" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="Q46" s="0" t="s">
         <x:v>30</x:v>
@@ -2698,10 +2731,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V46" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="W46" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:23">
@@ -2709,13 +2742,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G47" s="0">
         <x:v>0</x:v>
@@ -2733,19 +2766,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P47" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="Q47" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="Q47" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
       <x:c r="U47" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V47" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="W47" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:23">
@@ -2753,13 +2786,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G48" s="0">
         <x:v>0</x:v>
@@ -2777,19 +2810,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P48" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="Q48" s="0" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="Q48" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
       <x:c r="U48" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V48" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="W48" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:23">
@@ -2797,10 +2830,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>74</x:v>
@@ -2809,7 +2842,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="V49" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:23">
@@ -2817,13 +2850,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
         <x:v>53</x:v>
@@ -2844,7 +2877,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P50" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="Q50" s="0" t="s">
         <x:v>30</x:v>
@@ -2853,10 +2886,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V50" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="W50" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:23">
@@ -2864,13 +2897,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>43</x:v>
@@ -2891,19 +2924,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P51" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="Q51" s="0" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="Q51" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
       <x:c r="U51" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V51" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="W51" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:23">
@@ -2911,13 +2944,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
         <x:v>53</x:v>
@@ -2938,19 +2971,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P52" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="Q52" s="0" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="Q52" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
       <x:c r="U52" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V52" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="W52" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:23">
@@ -2958,16 +2991,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="U53" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V53" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:23">
@@ -2978,7 +3011,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>60</x:v>
@@ -3124,7 +3157,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="U58" s="0" t="s">
         <x:v>23</x:v>
@@ -3182,7 +3215,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="V60" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:23">
@@ -3190,13 +3223,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
         <x:v>53</x:v>
@@ -3217,7 +3250,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P61" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="Q61" s="0" t="s">
         <x:v>30</x:v>
@@ -3226,7 +3259,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V61" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="W61" s="0" t="s">
         <x:v>160</x:v>
@@ -3237,13 +3270,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
         <x:v>53</x:v>
@@ -3264,16 +3297,16 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P62" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q62" s="0" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="Q62" s="0" t="s">
-        <x:v>170</x:v>
-      </x:c>
       <x:c r="U62" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V62" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="W62" s="0" t="s">
         <x:v>160</x:v>
@@ -3284,13 +3317,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
         <x:v>53</x:v>
@@ -3311,16 +3344,16 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P63" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="Q63" s="0" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="Q63" s="0" t="s">
-        <x:v>174</x:v>
-      </x:c>
       <x:c r="U63" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V63" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="W63" s="0" t="s">
         <x:v>160</x:v>
@@ -3331,13 +3364,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
         <x:v>53</x:v>
@@ -3352,22 +3385,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L64" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="M64" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="P64" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="Q64" s="0" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="M64" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="P64" s="0" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="Q64" s="0" t="s">
-        <x:v>179</x:v>
-      </x:c>
       <x:c r="U64" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V64" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="W64" s="0" t="s">
         <x:v>160</x:v>
@@ -3378,13 +3411,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
         <x:v>43</x:v>
@@ -3393,16 +3426,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H65" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="Q65" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="U65" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V65" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="W65" s="0" t="s">
         <x:v>160</x:v>
@@ -3413,7 +3446,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>155</x:v>
@@ -3440,19 +3473,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P66" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="Q66" s="0" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="Q66" s="0" t="s">
-        <x:v>189</x:v>
-      </x:c>
       <x:c r="U66" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V66" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="W66" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:23">
@@ -3460,13 +3493,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
         <x:v>43</x:v>
@@ -3484,13 +3517,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L67" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="M67" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="P67" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="Q67" s="0" t="s">
         <x:v>30</x:v>
@@ -3499,10 +3532,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V67" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="W67" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:23">
@@ -3510,39 +3543,63 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D68" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="U68" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V68" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:23">
       <x:c r="A69" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="E69" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G69" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H69" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I69" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L69" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M69" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P69" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="Q69" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U69" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V69" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="W69" s="0" t="s">
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:23">
@@ -3550,13 +3607,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
         <x:v>53</x:v>
@@ -3577,19 +3634,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P70" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="Q70" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="U70" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V70" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="W70" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:23">
@@ -3597,13 +3654,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
         <x:v>53</x:v>
@@ -3624,19 +3681,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P71" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="Q71" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="U71" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V71" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="W71" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:23">
@@ -3644,13 +3701,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
         <x:v>53</x:v>
@@ -3665,25 +3722,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L72" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="M72" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="P72" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="Q72" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="U72" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V72" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="W72" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:23">
@@ -3691,63 +3748,54 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H73" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I73" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L73" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M73" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P73" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="Q73" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="U73" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V73" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="W73" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:23">
       <x:c r="A74" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F74" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>0</x:v>
@@ -3764,37 +3812,43 @@
       <x:c r="M74" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
+      <x:c r="O74" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
       <x:c r="P74" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="Q74" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U74" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V74" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="W74" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:23">
       <x:c r="A75" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F75" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>0</x:v>
@@ -3806,92 +3860,62 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L75" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="M75" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="P75" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="Q75" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U75" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V75" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="W75" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:23">
       <x:c r="A76" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="E76" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G76" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H76" s="0" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="I76" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L76" s="0" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="M76" s="0" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="P76" s="0" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="Q76" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="U76" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V76" s="0" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="W76" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:23">
       <x:c r="A77" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F77" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>0</x:v>
@@ -3903,45 +3927,42 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L77" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M77" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P77" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="Q77" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U77" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V77" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W77" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:23">
       <x:c r="A78" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F78" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G78" s="0">
         <x:v>0</x:v>
@@ -3959,19 +3980,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P78" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="Q78" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="U78" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V78" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W78" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:23">
@@ -3979,66 +4000,63 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H79" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I79" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="L79" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M79" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="P79" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="Q79" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="U79" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V79" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W79" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:23">
       <x:c r="A80" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F80" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>0</x:v>
@@ -4050,203 +4068,197 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L80" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="M80" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="P80" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="Q80" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="U80" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V80" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W80" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:23">
       <x:c r="A81" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F81" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="G81" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H81" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I81" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L81" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M81" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P81" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="Q81" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="U81" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V81" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W81" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:23">
       <x:c r="A82" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F82" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G82" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H82" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I82" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L82" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M82" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P82" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="Q82" s="0" t="s">
+        <x:v>190</x:v>
       </x:c>
       <x:c r="U82" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V82" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="W82" s="0" t="s">
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:23">
       <x:c r="A83" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F83" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G83" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H83" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I83" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L83" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="M83" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="P83" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="Q83" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U83" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V83" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="W83" s="0" t="s">
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:23">
       <x:c r="A84" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="G84" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H84" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I84" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L84" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M84" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P84" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="Q84" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="U84" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V84" s="0" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="W84" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:23">
       <x:c r="A85" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="G85" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H85" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I85" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L85" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M85" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P85" s="0" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="Q85" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="U85" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V85" s="0" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="W85" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:23">
@@ -4254,13 +4266,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>0</x:v>
@@ -4278,19 +4293,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P86" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="Q86" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="U86" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V86" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="W86" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:23">
@@ -4298,13 +4313,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="E87" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G87" s="0">
         <x:v>0</x:v>
@@ -4316,25 +4334,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L87" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M87" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="P87" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="Q87" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="U87" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V87" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="W87" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:23">
@@ -4342,13 +4360,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="E88" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G88" s="0">
         <x:v>0</x:v>
@@ -4360,62 +4381,119 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L88" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M88" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P88" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="Q88" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="U88" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V88" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="W88" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:23">
       <x:c r="A89" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G89" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H89" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I89" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L89" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M89" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P89" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="Q89" s="0" t="s">
+        <x:v>221</x:v>
       </x:c>
       <x:c r="U89" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V89" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="W89" s="0" t="s">
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:23">
       <x:c r="A90" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G90" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H90" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I90" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L90" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M90" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P90" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="Q90" s="0" t="s">
+        <x:v>224</x:v>
       </x:c>
       <x:c r="U90" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V90" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="W90" s="0" t="s">
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:23">
@@ -4423,13 +4501,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
         <x:v>53</x:v>
@@ -4440,17 +4518,29 @@
       <x:c r="H91" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="I91" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L91" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="M91" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="P91" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
       <x:c r="Q91" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="U91" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V91" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="W91" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:23">
@@ -4458,13 +4548,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
         <x:v>43</x:v>
@@ -4473,33 +4563,51 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H92" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="I92" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L92" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="M92" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="P92" s="0" t="s">
+        <x:v>232</x:v>
       </x:c>
       <x:c r="Q92" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="U92" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V92" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="W92" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:23">
       <x:c r="A93" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
+        <x:v>229</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F93" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G93" s="0">
         <x:v>0</x:v>
@@ -4507,37 +4615,79 @@
       <x:c r="H93" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="I93" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L93" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="M93" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="P93" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
       <x:c r="Q93" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="U93" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V93" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="W93" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:23">
       <x:c r="A94" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="E94" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F94" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G94" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H94" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I94" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L94" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M94" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P94" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="Q94" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U94" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V94" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="W94" s="0" t="s">
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:23">
@@ -4545,71 +4695,116 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="E95" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G95" s="0">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H95" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="I95" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L95" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="M95" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P95" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
       <x:c r="Q95" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="U95" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V95" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="W95" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:23">
       <x:c r="A96" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="E96" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F96" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G96" s="0">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H96" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I96" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L96" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="M96" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P96" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
       <x:c r="Q96" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="U96" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V96" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="W96" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:23">
       <x:c r="A97" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="E97" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F97" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G97" s="0">
         <x:v>0</x:v>
@@ -4627,7 +4822,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P97" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="Q97" s="0" t="s">
         <x:v>30</x:v>
@@ -4636,54 +4831,30 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V97" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="W97" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:23">
       <x:c r="A98" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="G98" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H98" s="0" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="I98" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L98" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M98" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P98" s="0" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="Q98" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="U98" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V98" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="W98" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:23">
@@ -4691,19 +4862,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="U99" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V99" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:23">
@@ -4711,28 +4882,43 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G100" s="0">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H100" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I100" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L100" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M100" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P100" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
       <x:c r="Q100" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="U100" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V100" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="W100" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:23">
@@ -4740,28 +4926,43 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="G101" s="0">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H101" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I101" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L101" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M101" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P101" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
       <x:c r="Q101" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="U101" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V101" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="W101" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:23">
@@ -4769,28 +4970,43 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="G102" s="0">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H102" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I102" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L102" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M102" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P102" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
       <x:c r="Q102" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="U102" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V102" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="W102" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:23">
@@ -4798,28 +5014,43 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H103" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I103" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L103" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="M103" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P103" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
       <x:c r="Q103" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="U103" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V103" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="W103" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:23">
@@ -4827,17 +5058,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="E104" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="G104" s="0">
         <x:v>0</x:v>
       </x:c>
@@ -4848,72 +5076,42 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L104" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="M104" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="P104" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="Q104" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="U104" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V104" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="W104" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:23">
       <x:c r="A105" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D105" s="0" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="E105" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G105" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H105" s="0" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="I105" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L105" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M105" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P105" s="0" t="s">
+      <x:c r="U105" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="V105" s="0" t="s">
         <x:v>262</x:v>
-      </x:c>
-      <x:c r="Q105" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="U105" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="V105" s="0" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="W105" s="0" t="s">
-        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:23">
@@ -4921,10 +5119,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>74</x:v>
@@ -4933,7 +5131,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="V106" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:23">
@@ -4941,13 +5139,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
         <x:v>53</x:v>
@@ -4958,18 +5156,6 @@
       <x:c r="H107" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I107" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L107" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M107" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P107" s="0" t="s">
-        <x:v>278</x:v>
-      </x:c>
       <x:c r="Q107" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
@@ -4977,10 +5163,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V107" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="W107" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:23">
@@ -4988,13 +5174,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
         <x:v>43</x:v>
@@ -5005,29 +5191,17 @@
       <x:c r="H108" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I108" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L108" s="0" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="M108" s="0" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="P108" s="0" t="s">
-        <x:v>284</x:v>
-      </x:c>
       <x:c r="Q108" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U108" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V108" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="W108" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:23">
@@ -5035,13 +5209,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D109" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
         <x:v>53</x:v>
@@ -5052,29 +5223,17 @@
       <x:c r="H109" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I109" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L109" s="0" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="M109" s="0" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="P109" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="Q109" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U109" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V109" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="W109" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:23">
@@ -5082,16 +5241,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U110" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V110" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:23">
@@ -5099,71 +5261,101 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G111" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H111" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="Q111" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="U111" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V111" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="W111" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:23">
       <x:c r="A112" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="G112" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q112" s="0" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="U112" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V112" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="W112" s="0" t="s">
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:23">
       <x:c r="A113" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G113" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H113" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I113" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L113" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M113" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P113" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="Q113" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U113" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V113" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="W113" s="0" t="s">
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:23">
@@ -5171,22 +5363,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="E114" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="G114" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H114" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="I114" s="0" t="s">
         <x:v>45</x:v>
@@ -5198,7 +5387,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P114" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="Q114" s="0" t="s">
         <x:v>30</x:v>
@@ -5207,57 +5396,30 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V114" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="W114" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:23">
       <x:c r="A115" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="E115" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G115" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H115" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I115" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L115" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M115" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P115" s="0" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="Q115" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="U115" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V115" s="0" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="W115" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:23">
@@ -5265,46 +5427,922 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G116" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q116" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="U116" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V116" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="W116" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:23">
+      <x:c r="A117" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="G117" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q117" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="U117" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V117" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="W117" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:23">
+      <x:c r="A118" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G118" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q118" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="U118" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V118" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="W118" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:23">
+      <x:c r="A119" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="G119" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q119" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="U119" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V119" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="W119" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:23">
+      <x:c r="A120" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D116" s="0" t="s">
+      <x:c r="D120" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="E120" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G120" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H120" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I120" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L120" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M120" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P120" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="Q120" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U120" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V120" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="W120" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:23">
+      <x:c r="A121" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E121" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G121" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H121" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="I121" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L121" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M121" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P121" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="Q121" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U121" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V121" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="W121" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:23">
+      <x:c r="A122" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="U122" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="V122" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:23">
+      <x:c r="A123" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E123" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G123" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H123" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I123" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L123" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M123" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P123" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="Q123" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U123" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V123" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="W123" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:23">
+      <x:c r="A124" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="E124" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G124" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H124" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I124" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L124" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="M124" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="P124" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="Q124" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="U124" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V124" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="W124" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:23">
+      <x:c r="A125" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E125" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G125" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H125" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I125" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L125" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="M125" s="0" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="P125" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="Q125" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="U125" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V125" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="W125" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:23">
+      <x:c r="A126" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="E116" s="0" t="s">
+      <x:c r="C126" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="U126" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="V126" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:23">
+      <x:c r="A127" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="G127" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H127" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q127" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U127" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V127" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="W127" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:23">
+      <x:c r="A128" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="U128" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="V128" s="0" t="s">
+        <x:v>302</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:23">
+      <x:c r="A129" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="U129" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="V129" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:23">
+      <x:c r="A130" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E130" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="G116" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H116" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I116" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L116" s="0" t="s">
+      <x:c r="G130" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H130" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I130" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L130" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="M116" s="0" t="s">
+      <x:c r="M130" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="P116" s="0" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="Q116" s="0" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="U116" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="V116" s="0" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="W116" s="0" t="s">
-        <x:v>294</x:v>
+      <x:c r="P130" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="Q130" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U130" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V130" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="W130" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:23">
+      <x:c r="A131" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="E131" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G131" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H131" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I131" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L131" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M131" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P131" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="Q131" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U131" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V131" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="W131" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:23">
+      <x:c r="A132" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E132" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G132" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H132" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I132" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L132" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M132" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P132" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="Q132" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="U132" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V132" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="W132" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:23">
+      <x:c r="A133" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="U133" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="V133" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:23">
+      <x:c r="A134" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E134" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G134" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H134" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I134" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L134" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M134" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P134" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="Q134" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U134" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V134" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="W134" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:23">
+      <x:c r="A135" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="E135" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G135" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H135" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I135" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L135" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M135" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P135" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="Q135" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U135" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V135" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="W135" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:23">
+      <x:c r="A136" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D136" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E136" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G136" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H136" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I136" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L136" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M136" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P136" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="Q136" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="U136" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V136" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="W136" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:23">
+      <x:c r="A137" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="U137" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="V137" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:23">
+      <x:c r="A138" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D138" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E138" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G138" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H138" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I138" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L138" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M138" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P138" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="Q138" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U138" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V138" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="W138" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:23">
+      <x:c r="A139" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="E139" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G139" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H139" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I139" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L139" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M139" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P139" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="Q139" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U139" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V139" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="W139" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:23">
+      <x:c r="A140" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E140" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G140" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H140" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I140" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L140" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M140" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P140" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="Q140" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="U140" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V140" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="W140" s="0" t="s">
+        <x:v>304</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Templates/Templates/Partlist.xlsx
+++ b/Templates/Templates/Partlist.xlsx
@@ -85,7 +85,7 @@
     <x:t>Power</x:t>
   </x:si>
   <x:si>
-    <x:t>ComponetItem</x:t>
+    <x:t>ComponentItem</x:t>
   </x:si>
   <x:si>
     <x:t>Akku-3300mAh</x:t>
@@ -505,7 +505,7 @@
     <x:t>The Wheel of the Robot</x:t>
   </x:si>
   <x:si>
-    <x:t>Mecanum-Wheel-left - Kopie</x:t>
+    <x:t>Mecanum-Wheel-left</x:t>
   </x:si>
   <x:si>
     <x:t>Wheel-Hub</x:t>
@@ -608,24 +608,6 @@
   </x:si>
   <x:si>
     <x:t>Mecanum_Rolle_1.stl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assembly: Mecanum-Wheel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mecanum-Wheel-left</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DHBW CAD-Data\MecanumWheel\STL-Step-Files\mecanumWheel_2b_pin24.stl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DHBW CAD-Data\OmniWheel\STL-Step-Dateien\Pin_Roller.stl</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>DHBW CAD-Data\MecanumWheel\STL-Step-Files\Mecanum_Rolle_1.stl</x:t>
   </x:si>
   <x:si>
     <x:t>mecanumWheel_1a_pin.stl</x:t>
@@ -1022,8 +1004,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartListTable" displayName="PartListTable" ref="A4:W140" totalsRowShown="0">
-  <x:autoFilter ref="A4:W140"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartListTable" displayName="PartListTable" ref="A4:W132" totalsRowShown="0">
+  <x:autoFilter ref="A4:W132"/>
   <x:tableColumns count="23">
     <x:tableColumn id="1" name="LEVEL"/>
     <x:tableColumn id="2" name="Name"/>
@@ -1341,13 +1323,13 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:W140"/>
+  <x:dimension ref="A1:W132"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="8.139196" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="25.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22.567768" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="15.282054" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="72.567768" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="47.282054" style="0" customWidth="1"/>
     <x:col min="5" max="6" width="12.567768" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="4.996339" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="32.139196" style="0" customWidth="1"/>
@@ -1363,8 +1345,8 @@
     <x:col min="18" max="18" width="13.424911" style="0" customWidth="1"/>
     <x:col min="19" max="20" width="12.282054" style="0" customWidth="1"/>
     <x:col min="21" max="21" width="18.282054" style="0" customWidth="1"/>
-    <x:col min="22" max="22" width="26.424911" style="0" customWidth="1"/>
-    <x:col min="23" max="23" width="25.996339" style="0" customWidth="1"/>
+    <x:col min="22" max="22" width="19.853482" style="0" customWidth="1"/>
+    <x:col min="23" max="23" width="16.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="4" spans="1:23">
@@ -1423,10 +1405,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="T4" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="U4" s="0" t="s">
         <x:v>18</x:v>
@@ -3543,16 +3525,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>162</x:v>
       </x:c>
       <x:c r="U68" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V68" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:23">
@@ -3596,10 +3581,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V69" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W69" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:23">
@@ -3634,7 +3619,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P70" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="Q70" s="0" t="s">
         <x:v>171</x:v>
@@ -3643,10 +3628,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V70" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W70" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:23">
@@ -3660,7 +3645,7 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
         <x:v>53</x:v>
@@ -3681,7 +3666,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P71" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="Q71" s="0" t="s">
         <x:v>175</x:v>
@@ -3690,10 +3675,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V71" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W71" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:23">
@@ -3737,10 +3722,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V72" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W72" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:23">
@@ -3763,7 +3748,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H73" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="Q73" s="0" t="s">
         <x:v>188</x:v>
@@ -3772,10 +3757,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V73" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W73" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:23">
@@ -3789,10 +3774,7 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="E74" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
         <x:v>43</x:v>
@@ -3812,20 +3794,17 @@
       <x:c r="M74" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="O74" s="0" t="s">
-        <x:v>202</x:v>
-      </x:c>
       <x:c r="P74" s="0" t="s">
         <x:v>191</x:v>
       </x:c>
       <x:c r="Q74" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="U74" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V74" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W74" s="0" t="s">
         <x:v>184</x:v>
@@ -3842,7 +3821,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
         <x:v>43</x:v>
@@ -3875,7 +3854,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V75" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W75" s="0" t="s">
         <x:v>184</x:v>
@@ -3886,66 +3865,39 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="U76" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V76" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:23">
       <x:c r="A77" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="E77" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G77" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H77" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I77" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L77" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M77" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P77" s="0" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="Q77" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="U77" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V77" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="W77" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:23">
@@ -3953,13 +3905,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
         <x:v>53</x:v>
@@ -3980,19 +3932,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P78" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="Q78" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="U78" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V78" s="0" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="Q78" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="U78" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="V78" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
       <x:c r="W78" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:23">
@@ -4000,13 +3952,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>174</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
         <x:v>53</x:v>
@@ -4027,19 +3979,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P79" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="Q79" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="U79" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V79" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="W79" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:23">
@@ -4047,13 +3999,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
         <x:v>53</x:v>
@@ -4068,25 +4020,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L80" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M80" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P80" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="Q80" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="U80" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V80" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="W80" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:23">
@@ -4094,51 +4046,63 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G81" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H81" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I81" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L81" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M81" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P81" s="0" t="s">
+        <x:v>216</x:v>
       </x:c>
       <x:c r="Q81" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="U81" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V81" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="W81" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:23">
       <x:c r="A82" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F82" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="E82" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G82" s="0">
         <x:v>0</x:v>
@@ -4156,39 +4120,36 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P82" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="Q82" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="U82" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V82" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="W82" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:23">
       <x:c r="A83" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F83" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G83" s="0">
         <x:v>0</x:v>
@@ -4200,82 +4161,142 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L83" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="M83" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="P83" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="Q83" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="U83" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V83" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="W83" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:23">
       <x:c r="A84" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G84" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H84" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="I84" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L84" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="M84" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="P84" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="Q84" s="0" t="s">
+        <x:v>225</x:v>
       </x:c>
       <x:c r="U84" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V84" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="W84" s="0" t="s">
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:23">
       <x:c r="A85" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="E85" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F85" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G85" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H85" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I85" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L85" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="M85" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="P85" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="Q85" s="0" t="s">
+        <x:v>227</x:v>
       </x:c>
       <x:c r="U85" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V85" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="W85" s="0" t="s">
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:23">
       <x:c r="A86" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F86" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>0</x:v>
@@ -4293,19 +4314,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P86" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="Q86" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U86" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V86" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="W86" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:23">
@@ -4313,63 +4334,66 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G87" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H87" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="I87" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="L87" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="M87" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="P87" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="Q87" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="U87" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V87" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="W87" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:23">
       <x:c r="A88" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F88" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G88" s="0">
         <x:v>0</x:v>
@@ -4381,42 +4405,45 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L88" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="M88" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="P88" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="Q88" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="U88" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V88" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="W88" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:23">
       <x:c r="A89" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F89" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G89" s="0">
         <x:v>0</x:v>
@@ -4434,113 +4461,59 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P89" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="Q89" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U89" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V89" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="W89" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:23">
       <x:c r="A90" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="E90" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G90" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H90" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I90" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L90" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M90" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P90" s="0" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="Q90" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="U90" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V90" s="0" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="W90" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:23">
       <x:c r="A91" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="E91" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G91" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H91" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I91" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L91" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="M91" s="0" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="P91" s="0" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="Q91" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="U91" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V91" s="0" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="W91" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:23">
@@ -4548,66 +4521,57 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="E92" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G92" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H92" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I92" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="L92" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M92" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P92" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="Q92" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="U92" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V92" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="W92" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:23">
       <x:c r="A93" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="E93" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F93" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="G93" s="0">
         <x:v>0</x:v>
@@ -4619,45 +4583,39 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L93" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M93" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P93" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="Q93" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="U93" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V93" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="W93" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:23">
       <x:c r="A94" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="E94" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F94" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="G94" s="0">
         <x:v>0</x:v>
@@ -4675,19 +4633,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P94" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="Q94" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="U94" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V94" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="W94" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:23">
@@ -4695,66 +4653,57 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="E95" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G95" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H95" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I95" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="L95" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="M95" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="P95" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="Q95" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="U95" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V95" s="0" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="U95" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="V95" s="0" t="s">
-        <x:v>210</x:v>
-      </x:c>
       <x:c r="W95" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:23">
       <x:c r="A96" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>193</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="E96" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F96" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G96" s="0">
         <x:v>0</x:v>
@@ -4769,72 +4718,39 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="M96" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="P96" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="Q96" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="U96" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V96" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="W96" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:23">
       <x:c r="A97" s="0">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D97" s="0" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="E97" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F97" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G97" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H97" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I97" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L97" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M97" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P97" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="Q97" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="U97" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V97" s="0" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="W97" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:23">
@@ -4842,39 +4758,54 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="U98" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="V98" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:23">
       <x:c r="A99" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E99" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G99" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H99" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q99" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U99" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V99" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="W99" s="0" t="s">
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:23">
@@ -4882,13 +4813,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E100" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G100" s="0">
         <x:v>0</x:v>
@@ -4896,29 +4830,17 @@
       <x:c r="H100" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I100" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L100" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M100" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P100" s="0" t="s">
-        <x:v>246</x:v>
-      </x:c>
       <x:c r="Q100" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U100" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V100" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="W100" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:23">
@@ -4926,13 +4848,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="D101" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E101" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G101" s="0">
         <x:v>0</x:v>
@@ -4940,73 +4862,37 @@
       <x:c r="H101" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I101" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L101" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M101" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P101" s="0" t="s">
-        <x:v>250</x:v>
-      </x:c>
       <x:c r="Q101" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U101" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V101" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="W101" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:23">
       <x:c r="A102" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="G102" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H102" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I102" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L102" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M102" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P102" s="0" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="Q102" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U102" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V102" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="W102" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:23">
@@ -5014,43 +4900,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H103" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I103" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L103" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="M103" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P103" s="0" t="s">
-        <x:v>183</x:v>
-      </x:c>
       <x:c r="Q103" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="U103" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V103" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="W103" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:23">
@@ -5058,115 +4929,136 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G104" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H104" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I104" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L104" s="0" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="M104" s="0" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="P104" s="0" t="s">
-        <x:v>259</x:v>
-      </x:c>
       <x:c r="Q104" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="U104" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V104" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="W104" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:23">
       <x:c r="A105" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>260</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
         <x:v>261</x:v>
       </x:c>
+      <x:c r="G105" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H105" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I105" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L105" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M105" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P105" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="Q105" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="U105" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V105" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="W105" s="0" t="s">
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:23">
       <x:c r="A106" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>263</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="D106" s="0" t="s">
-        <x:v>74</x:v>
+      <x:c r="G106" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H106" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="I106" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L106" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M106" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P106" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="Q106" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U106" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V106" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="W106" s="0" t="s">
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:23">
       <x:c r="A107" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="E107" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G107" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H107" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="Q107" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="U107" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V107" s="0" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="W107" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:23">
@@ -5174,34 +5066,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="E108" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="G108" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H108" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="Q108" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="U108" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V108" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="W108" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:23">
@@ -5209,51 +5095,57 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E109" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
+        <x:v>271</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H109" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="Q109" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="U109" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V109" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="W109" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:23">
       <x:c r="A110" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G110" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q110" s="0" t="s">
+        <x:v>275</x:v>
       </x:c>
       <x:c r="U110" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V110" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="W110" s="0" t="s">
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:23">
@@ -5261,28 +5153,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="G111" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q111" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="U111" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V111" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="W111" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:23">
@@ -5290,28 +5182,46 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="E112" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H112" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I112" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L112" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M112" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P112" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
       <x:c r="Q112" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U112" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V112" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="W112" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:23">
@@ -5319,19 +5229,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="E113" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G113" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H113" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="I113" s="0" t="s">
         <x:v>45</x:v>
@@ -5343,7 +5256,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P113" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="Q113" s="0" t="s">
         <x:v>30</x:v>
@@ -5352,74 +5265,77 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V113" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="W113" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:23">
       <x:c r="A114" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="G114" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H114" s="0" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="I114" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L114" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M114" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P114" s="0" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="Q114" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="U114" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V114" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="W114" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:23">
       <x:c r="A115" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E115" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G115" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H115" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I115" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L115" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M115" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P115" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="Q115" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U115" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V115" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="W115" s="0" t="s">
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:23">
@@ -5427,28 +5343,46 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="E116" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G116" s="0">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H116" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I116" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L116" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="M116" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="P116" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
       <x:c r="Q116" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="U116" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V116" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="W116" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:23">
@@ -5456,57 +5390,63 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="E117" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H117" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I117" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L117" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="M117" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="P117" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
       <x:c r="Q117" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="U117" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V117" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="W117" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:23">
       <x:c r="A118" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D118" s="0" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="G118" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q118" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="U118" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V118" s="0" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="W118" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:23">
@@ -5514,142 +5454,118 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="G119" s="0">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H119" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
       <x:c r="Q119" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U119" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V119" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="W119" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>293</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:23">
       <x:c r="A120" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="E120" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G120" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H120" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I120" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L120" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M120" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P120" s="0" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="Q120" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="U120" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V120" s="0" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="W120" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:23">
       <x:c r="A121" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="E121" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G121" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H121" s="0" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="I121" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L121" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M121" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P121" s="0" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="Q121" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="U121" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V121" s="0" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="W121" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:23">
       <x:c r="A122" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E122" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G122" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H122" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I122" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L122" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M122" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P122" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="Q122" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U122" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V122" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="W122" s="0" t="s">
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:23">
@@ -5657,16 +5573,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G123" s="0">
         <x:v>0</x:v>
@@ -5684,7 +5600,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P123" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="Q123" s="0" t="s">
         <x:v>30</x:v>
@@ -5693,10 +5609,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V123" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="W123" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:23">
@@ -5704,16 +5620,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G124" s="0">
         <x:v>0</x:v>
@@ -5725,89 +5641,92 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L124" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M124" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P124" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="Q124" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="U124" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V124" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="W124" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:23">
       <x:c r="A125" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="E125" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G125" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H125" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I125" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L125" s="0" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="M125" s="0" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="P125" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="Q125" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="U125" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="V125" s="0" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="W125" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:23">
       <x:c r="A126" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E126" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G126" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H126" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I126" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L126" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M126" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P126" s="0" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="C126" s="0" t="s">
-        <x:v>35</x:v>
+      <x:c r="Q126" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U126" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V126" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="W126" s="0" t="s">
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:23">
@@ -5815,19 +5734,34 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G127" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H127" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I127" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L127" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M127" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P127" s="0" t="s">
         <x:v>301</x:v>
-      </x:c>
-      <x:c r="G127" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H127" s="0" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="Q127" s="0" t="s">
         <x:v>30</x:v>
@@ -5836,30 +5770,57 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V127" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="W127" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:23">
       <x:c r="A128" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="C128" s="0" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="D128" s="0" t="s">
+      <x:c r="E128" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G128" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H128" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I128" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L128" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M128" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P128" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="Q128" s="0" t="s">
         <x:v>303</x:v>
       </x:c>
       <x:c r="U128" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V128" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="W128" s="0" t="s">
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:23">
@@ -5867,7 +5828,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>132</x:v>
@@ -5879,7 +5840,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="V129" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:23">
@@ -5914,7 +5875,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P130" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="Q130" s="0" t="s">
         <x:v>30</x:v>
@@ -5923,10 +5884,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V130" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="W130" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:23">
@@ -5940,7 +5901,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
         <x:v>43</x:v>
@@ -5961,7 +5922,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P131" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="Q131" s="0" t="s">
         <x:v>30</x:v>
@@ -5970,10 +5931,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V131" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="W131" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:23">
@@ -5987,7 +5948,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
         <x:v>53</x:v>
@@ -6008,341 +5969,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P132" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="Q132" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="U132" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V132" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="W132" s="0" t="s">
-        <x:v>304</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" spans="1:23">
-      <x:c r="A133" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B133" s="0" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="C133" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D133" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="U133" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="V133" s="0" t="s">
-        <x:v>311</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" spans="1:23">
-      <x:c r="A134" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="C134" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D134" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="E134" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G134" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H134" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I134" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L134" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M134" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P134" s="0" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="Q134" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="U134" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="V134" s="0" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="W134" s="0" t="s">
-        <x:v>304</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="135" spans="1:23">
-      <x:c r="A135" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="C135" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D135" s="0" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="E135" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G135" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H135" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I135" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L135" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M135" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P135" s="0" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="Q135" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="U135" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="V135" s="0" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="W135" s="0" t="s">
-        <x:v>304</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="136" spans="1:23">
-      <x:c r="A136" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B136" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C136" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D136" s="0" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="E136" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G136" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H136" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I136" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L136" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M136" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P136" s="0" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="Q136" s="0" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="U136" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="V136" s="0" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="W136" s="0" t="s">
-        <x:v>304</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" spans="1:23">
-      <x:c r="A137" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B137" s="0" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="C137" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D137" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="U137" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="V137" s="0" t="s">
-        <x:v>312</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="138" spans="1:23">
-      <x:c r="A138" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B138" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="C138" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D138" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="E138" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G138" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H138" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I138" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L138" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M138" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P138" s="0" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="Q138" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="U138" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="V138" s="0" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="W138" s="0" t="s">
-        <x:v>304</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="139" spans="1:23">
-      <x:c r="A139" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B139" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="C139" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D139" s="0" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="E139" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G139" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H139" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I139" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L139" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M139" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P139" s="0" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="Q139" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="U139" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="V139" s="0" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="W139" s="0" t="s">
-        <x:v>304</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="140" spans="1:23">
-      <x:c r="A140" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B140" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C140" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D140" s="0" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="E140" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G140" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H140" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I140" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L140" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="M140" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P140" s="0" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="Q140" s="0" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="U140" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="V140" s="0" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="W140" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Templates/Templates/Partlist.xlsx
+++ b/Templates/Templates/Partlist.xlsx
@@ -910,6 +910,9 @@
     <x:t>The Comunication Platform for Micro Ros</x:t>
   </x:si>
   <x:si>
+    <x:t>US-Sensor smal</x:t>
+  </x:si>
+  <x:si>
     <x:t>US-Sensor</x:t>
   </x:si>
   <x:si>
@@ -931,7 +934,13 @@
     <x:t>SensorTopUS.stl</x:t>
   </x:si>
   <x:si>
+    <x:t>US-Sensor Single 16</x:t>
+  </x:si>
+  <x:si>
     <x:t>US_Sensor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US-Sensor hc_sr04</x:t>
   </x:si>
   <x:si>
     <x:t>US_Sensor_hc_Sr04</x:t>
@@ -1346,7 +1355,7 @@
     <x:col min="19" max="20" width="12.282054" style="0" customWidth="1"/>
     <x:col min="21" max="21" width="18.282054" style="0" customWidth="1"/>
     <x:col min="22" max="22" width="19.853482" style="0" customWidth="1"/>
-    <x:col min="23" max="23" width="16.853482" style="0" customWidth="1"/>
+    <x:col min="23" max="23" width="18.424911" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="4" spans="1:23">
@@ -1405,10 +1414,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="T4" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="U4" s="0" t="s">
         <x:v>18</x:v>
@@ -5518,7 +5527,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="V121" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:23">
@@ -5553,7 +5562,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P122" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="Q122" s="0" t="s">
         <x:v>30</x:v>
@@ -5562,7 +5571,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V122" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="W122" s="0" t="s">
         <x:v>298</x:v>
@@ -5579,7 +5588,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
         <x:v>43</x:v>
@@ -5600,7 +5609,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P123" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="Q123" s="0" t="s">
         <x:v>30</x:v>
@@ -5609,7 +5618,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V123" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="W123" s="0" t="s">
         <x:v>298</x:v>
@@ -5626,7 +5635,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
         <x:v>53</x:v>
@@ -5647,16 +5656,16 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P124" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="Q124" s="0" t="s">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="Q124" s="0" t="s">
-        <x:v>303</x:v>
-      </x:c>
       <x:c r="U124" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V124" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="W124" s="0" t="s">
         <x:v>298</x:v>
@@ -5667,7 +5676,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>132</x:v>
@@ -5679,7 +5688,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="V125" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>307</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:23">
@@ -5714,7 +5723,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P126" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="Q126" s="0" t="s">
         <x:v>30</x:v>
@@ -5723,10 +5732,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V126" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="W126" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:23">
@@ -5740,7 +5749,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
         <x:v>43</x:v>
@@ -5761,7 +5770,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P127" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="Q127" s="0" t="s">
         <x:v>30</x:v>
@@ -5770,10 +5779,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V127" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="W127" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:23">
@@ -5787,7 +5796,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
         <x:v>53</x:v>
@@ -5808,19 +5817,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P128" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="Q128" s="0" t="s">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="Q128" s="0" t="s">
-        <x:v>303</x:v>
-      </x:c>
       <x:c r="U128" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V128" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="W128" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:23">
@@ -5828,7 +5837,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>132</x:v>
@@ -5840,7 +5849,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="V129" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:23">
@@ -5875,7 +5884,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P130" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="Q130" s="0" t="s">
         <x:v>30</x:v>
@@ -5884,10 +5893,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V130" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="W130" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:23">
@@ -5901,7 +5910,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
         <x:v>43</x:v>
@@ -5922,7 +5931,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P131" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="Q131" s="0" t="s">
         <x:v>30</x:v>
@@ -5931,10 +5940,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V131" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="W131" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:23">
@@ -5948,7 +5957,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
         <x:v>53</x:v>
@@ -5969,19 +5978,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P132" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="Q132" s="0" t="s">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="Q132" s="0" t="s">
-        <x:v>303</x:v>
-      </x:c>
       <x:c r="U132" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V132" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="W132" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
